--- a/exploratory_study_2/recover_terms.xlsx
+++ b/exploratory_study_2/recover_terms.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glori\Documents\Persönliches\#PhD_local\code\reddit_bd_recovery\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glori\Documents\Persönliches\#PhD_local\code\reddit_bd_recovery\exploratory_study_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C659DF9-39F6-41DC-A85E-E73B9FB7E75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A31B25-6E3D-41BB-814E-BE0341659D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2212,9 +2212,6 @@
     <t>terms_recover_not_recover</t>
   </si>
   <si>
-    <t>Terms from "terms_recover" that are (part of) an url</t>
-  </si>
-  <si>
     <t>Terms from "terms_recover" that constitute a proper name</t>
   </si>
   <si>
@@ -2225,6 +2222,9 @@
   </si>
   <si>
     <t>The 159 unique *recover* content terms used to create the *recover* corpus (urls, proper names and terms that do not have *recover* as a stem removed) (Step 2)</t>
+  </si>
+  <si>
+    <t>Terms from "terms_recover" that are (part of) an url - partly automatically identified via regular expression</t>
   </si>
 </sst>
 </file>
@@ -3106,7 +3106,7 @@
         <v>720</v>
       </c>
       <c r="B3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3114,7 +3114,7 @@
         <v>721</v>
       </c>
       <c r="B4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3122,7 @@
         <v>722</v>
       </c>
       <c r="B5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3130,7 +3130,7 @@
         <v>723</v>
       </c>
       <c r="B6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3138,7 @@
         <v>724</v>
       </c>
       <c r="B7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
